--- a/Lab2 LFSR/Тест ЛР2 LFSR28 (x^28+x^3+1) 60 итераций seed=111...1.xlsx
+++ b/Lab2 LFSR/Тест ЛР2 LFSR28 (x^28+x^3+1) 60 итераций seed=111...1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programs\Microsoft Visual Studio\Projects\Information-theory\Lab2 LFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2592018E-418A-4EED-94A3-2B059A7F4901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4DBEAA-B84C-4238-A164-D79A3C166DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,6 +145,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -154,12 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,36 +475,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:34" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
+      <c r="D1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
       <c r="AG1" s="2" t="s">
         <v>1</v>
       </c>
@@ -590,26 +590,26 @@
       <c r="AB2" s="3">
         <v>4</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="AC2" s="6">
         <v>3</v>
       </c>
       <c r="AD2" s="3">
         <v>2</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AE2" s="6">
         <v>1</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
     </row>
     <row r="3" spans="2:34" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
       <c r="E3" s="5">
@@ -684,28 +684,28 @@
       <c r="AB3" s="5">
         <v>1</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AC3" s="6">
         <v>1</v>
       </c>
       <c r="AD3" s="5">
         <v>1</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AE3" s="6">
         <v>1</v>
       </c>
       <c r="AG3" s="5">
         <v>0</v>
       </c>
-      <c r="AH3" s="12">
+      <c r="AH3" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B4" s="9"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="7">
         <v>1</v>
       </c>
       <c r="E4" s="5">
@@ -780,28 +780,28 @@
       <c r="AB4" s="5">
         <v>1</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AC4" s="6">
         <v>1</v>
       </c>
       <c r="AD4" s="5">
         <v>1</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AE4" s="6">
         <v>0</v>
       </c>
       <c r="AG4" s="5">
         <v>1</v>
       </c>
-      <c r="AH4" s="12">
+      <c r="AH4" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B5" s="9"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="5">
         <v>3</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="7">
         <v>1</v>
       </c>
       <c r="E5" s="5">
@@ -876,28 +876,28 @@
       <c r="AB5" s="5">
         <v>1</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AC5" s="6">
         <v>1</v>
       </c>
       <c r="AD5" s="5">
         <v>0</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="6">
         <v>1</v>
       </c>
       <c r="AG5" s="5">
         <v>0</v>
       </c>
-      <c r="AH5" s="12">
+      <c r="AH5" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B6" s="9"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="5">
         <v>4</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="7">
         <v>1</v>
       </c>
       <c r="E6" s="5">
@@ -972,28 +972,28 @@
       <c r="AB6" s="5">
         <v>1</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AC6" s="6">
         <v>0</v>
       </c>
       <c r="AD6" s="5">
         <v>1</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AE6" s="6">
         <v>0</v>
       </c>
       <c r="AG6" s="5">
         <v>0</v>
       </c>
-      <c r="AH6" s="12">
+      <c r="AH6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B7" s="9"/>
+      <c r="B7" s="11"/>
       <c r="C7" s="5">
         <v>5</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="7">
         <v>1</v>
       </c>
       <c r="E7" s="5">
@@ -1068,28 +1068,28 @@
       <c r="AB7" s="5">
         <v>0</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AC7" s="6">
         <v>1</v>
       </c>
       <c r="AD7" s="5">
         <v>0</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AE7" s="6">
         <v>0</v>
       </c>
       <c r="AG7" s="5">
         <v>1</v>
       </c>
-      <c r="AH7" s="12">
+      <c r="AH7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B8" s="9"/>
+      <c r="B8" s="11"/>
       <c r="C8" s="5">
         <v>6</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="7">
         <v>1</v>
       </c>
       <c r="E8" s="5">
@@ -1164,28 +1164,28 @@
       <c r="AB8" s="5">
         <v>1</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AC8" s="6">
         <v>0</v>
       </c>
       <c r="AD8" s="5">
         <v>0</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AE8" s="6">
         <v>1</v>
       </c>
       <c r="AG8" s="5">
         <v>1</v>
       </c>
-      <c r="AH8" s="12">
+      <c r="AH8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B9" s="9"/>
+      <c r="B9" s="11"/>
       <c r="C9" s="5">
         <v>7</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="7">
         <v>1</v>
       </c>
       <c r="E9" s="5">
@@ -1260,28 +1260,28 @@
       <c r="AB9" s="5">
         <v>0</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AC9" s="6">
         <v>0</v>
       </c>
       <c r="AD9" s="5">
         <v>1</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AE9" s="6">
         <v>1</v>
       </c>
       <c r="AG9" s="5">
         <v>1</v>
       </c>
-      <c r="AH9" s="12">
+      <c r="AH9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B10" s="9"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="5">
         <v>8</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="7">
         <v>1</v>
       </c>
       <c r="E10" s="5">
@@ -1356,28 +1356,28 @@
       <c r="AB10" s="5">
         <v>0</v>
       </c>
-      <c r="AC10" s="11">
+      <c r="AC10" s="6">
         <v>1</v>
       </c>
       <c r="AD10" s="5">
         <v>1</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AE10" s="6">
         <v>1</v>
       </c>
       <c r="AG10" s="5">
         <v>0</v>
       </c>
-      <c r="AH10" s="12">
+      <c r="AH10" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B11" s="9"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="5">
         <v>9</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="7">
         <v>1</v>
       </c>
       <c r="E11" s="5">
@@ -1452,28 +1452,28 @@
       <c r="AB11" s="5">
         <v>1</v>
       </c>
-      <c r="AC11" s="11">
+      <c r="AC11" s="6">
         <v>1</v>
       </c>
       <c r="AD11" s="5">
         <v>1</v>
       </c>
-      <c r="AE11" s="11">
+      <c r="AE11" s="6">
         <v>0</v>
       </c>
       <c r="AG11" s="5">
         <v>1</v>
       </c>
-      <c r="AH11" s="12">
+      <c r="AH11" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B12" s="9"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="5">
         <v>10</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="7">
         <v>1</v>
       </c>
       <c r="E12" s="5">
@@ -1548,28 +1548,28 @@
       <c r="AB12" s="5">
         <v>1</v>
       </c>
-      <c r="AC12" s="11">
+      <c r="AC12" s="6">
         <v>1</v>
       </c>
       <c r="AD12" s="5">
         <v>0</v>
       </c>
-      <c r="AE12" s="11">
+      <c r="AE12" s="6">
         <v>1</v>
       </c>
       <c r="AG12" s="5">
         <v>0</v>
       </c>
-      <c r="AH12" s="12">
+      <c r="AH12" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B13" s="9"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="5">
         <v>11</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="7">
         <v>1</v>
       </c>
       <c r="E13" s="5">
@@ -1644,28 +1644,28 @@
       <c r="AB13" s="5">
         <v>1</v>
       </c>
-      <c r="AC13" s="11">
+      <c r="AC13" s="6">
         <v>0</v>
       </c>
       <c r="AD13" s="5">
         <v>1</v>
       </c>
-      <c r="AE13" s="11">
+      <c r="AE13" s="6">
         <v>0</v>
       </c>
       <c r="AG13" s="5">
         <v>0</v>
       </c>
-      <c r="AH13" s="12">
+      <c r="AH13" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B14" s="9"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="5">
         <v>12</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="7">
         <v>1</v>
       </c>
       <c r="E14" s="5">
@@ -1740,28 +1740,28 @@
       <c r="AB14" s="5">
         <v>0</v>
       </c>
-      <c r="AC14" s="11">
+      <c r="AC14" s="6">
         <v>1</v>
       </c>
       <c r="AD14" s="5">
         <v>0</v>
       </c>
-      <c r="AE14" s="11">
+      <c r="AE14" s="6">
         <v>0</v>
       </c>
       <c r="AG14" s="5">
         <v>1</v>
       </c>
-      <c r="AH14" s="12">
+      <c r="AH14" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="5">
         <v>13</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="7">
         <v>1</v>
       </c>
       <c r="E15" s="5">
@@ -1836,28 +1836,28 @@
       <c r="AB15" s="5">
         <v>1</v>
       </c>
-      <c r="AC15" s="11">
+      <c r="AC15" s="6">
         <v>0</v>
       </c>
       <c r="AD15" s="5">
         <v>0</v>
       </c>
-      <c r="AE15" s="11">
+      <c r="AE15" s="6">
         <v>1</v>
       </c>
       <c r="AG15" s="5">
         <v>1</v>
       </c>
-      <c r="AH15" s="12">
+      <c r="AH15" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="5">
         <v>14</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="7">
         <v>1</v>
       </c>
       <c r="E16" s="5">
@@ -1932,28 +1932,28 @@
       <c r="AB16" s="5">
         <v>0</v>
       </c>
-      <c r="AC16" s="11">
+      <c r="AC16" s="6">
         <v>0</v>
       </c>
       <c r="AD16" s="5">
         <v>1</v>
       </c>
-      <c r="AE16" s="11">
+      <c r="AE16" s="6">
         <v>1</v>
       </c>
       <c r="AG16" s="5">
         <v>1</v>
       </c>
-      <c r="AH16" s="12">
+      <c r="AH16" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="5">
         <v>15</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="7">
         <v>1</v>
       </c>
       <c r="E17" s="5">
@@ -2028,28 +2028,28 @@
       <c r="AB17" s="5">
         <v>0</v>
       </c>
-      <c r="AC17" s="11">
+      <c r="AC17" s="6">
         <v>1</v>
       </c>
       <c r="AD17" s="5">
         <v>1</v>
       </c>
-      <c r="AE17" s="11">
+      <c r="AE17" s="6">
         <v>1</v>
       </c>
       <c r="AG17" s="5">
         <v>0</v>
       </c>
-      <c r="AH17" s="12">
+      <c r="AH17" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B18" s="9"/>
+      <c r="B18" s="11"/>
       <c r="C18" s="5">
         <v>16</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="7">
         <v>1</v>
       </c>
       <c r="E18" s="5">
@@ -2124,28 +2124,28 @@
       <c r="AB18" s="5">
         <v>1</v>
       </c>
-      <c r="AC18" s="11">
+      <c r="AC18" s="6">
         <v>1</v>
       </c>
       <c r="AD18" s="5">
         <v>1</v>
       </c>
-      <c r="AE18" s="11">
+      <c r="AE18" s="6">
         <v>0</v>
       </c>
       <c r="AG18" s="5">
         <v>1</v>
       </c>
-      <c r="AH18" s="12">
+      <c r="AH18" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="5">
         <v>17</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="7">
         <v>1</v>
       </c>
       <c r="E19" s="5">
@@ -2220,28 +2220,28 @@
       <c r="AB19" s="5">
         <v>1</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="AC19" s="6">
         <v>1</v>
       </c>
       <c r="AD19" s="5">
         <v>0</v>
       </c>
-      <c r="AE19" s="11">
+      <c r="AE19" s="6">
         <v>1</v>
       </c>
       <c r="AG19" s="5">
         <v>0</v>
       </c>
-      <c r="AH19" s="12">
+      <c r="AH19" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="5">
         <v>18</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="7">
         <v>1</v>
       </c>
       <c r="E20" s="5">
@@ -2316,28 +2316,28 @@
       <c r="AB20" s="5">
         <v>1</v>
       </c>
-      <c r="AC20" s="11">
+      <c r="AC20" s="6">
         <v>0</v>
       </c>
       <c r="AD20" s="5">
         <v>1</v>
       </c>
-      <c r="AE20" s="11">
+      <c r="AE20" s="6">
         <v>0</v>
       </c>
       <c r="AG20" s="5">
         <v>0</v>
       </c>
-      <c r="AH20" s="12">
+      <c r="AH20" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B21" s="9"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="5">
         <v>19</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="7">
         <v>1</v>
       </c>
       <c r="E21" s="5">
@@ -2412,28 +2412,28 @@
       <c r="AB21" s="5">
         <v>0</v>
       </c>
-      <c r="AC21" s="11">
+      <c r="AC21" s="6">
         <v>1</v>
       </c>
       <c r="AD21" s="5">
         <v>0</v>
       </c>
-      <c r="AE21" s="11">
+      <c r="AE21" s="6">
         <v>0</v>
       </c>
       <c r="AG21" s="5">
         <v>1</v>
       </c>
-      <c r="AH21" s="12">
+      <c r="AH21" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B22" s="9"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="5">
         <v>20</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="7">
         <v>1</v>
       </c>
       <c r="E22" s="5">
@@ -2508,28 +2508,28 @@
       <c r="AB22" s="5">
         <v>1</v>
       </c>
-      <c r="AC22" s="11">
+      <c r="AC22" s="6">
         <v>0</v>
       </c>
       <c r="AD22" s="5">
         <v>0</v>
       </c>
-      <c r="AE22" s="11">
+      <c r="AE22" s="6">
         <v>1</v>
       </c>
       <c r="AG22" s="5">
         <v>1</v>
       </c>
-      <c r="AH22" s="12">
+      <c r="AH22" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B23" s="9"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="5">
         <v>21</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="7">
         <v>1</v>
       </c>
       <c r="E23" s="5">
@@ -2604,28 +2604,28 @@
       <c r="AB23" s="5">
         <v>0</v>
       </c>
-      <c r="AC23" s="11">
+      <c r="AC23" s="6">
         <v>0</v>
       </c>
       <c r="AD23" s="5">
         <v>1</v>
       </c>
-      <c r="AE23" s="11">
+      <c r="AE23" s="6">
         <v>1</v>
       </c>
       <c r="AG23" s="5">
         <v>1</v>
       </c>
-      <c r="AH23" s="12">
+      <c r="AH23" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B24" s="9"/>
+      <c r="B24" s="11"/>
       <c r="C24" s="5">
         <v>22</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="7">
         <v>1</v>
       </c>
       <c r="E24" s="5">
@@ -2700,28 +2700,28 @@
       <c r="AB24" s="5">
         <v>0</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="AC24" s="6">
         <v>1</v>
       </c>
       <c r="AD24" s="5">
         <v>1</v>
       </c>
-      <c r="AE24" s="11">
+      <c r="AE24" s="6">
         <v>1</v>
       </c>
       <c r="AG24" s="5">
         <v>0</v>
       </c>
-      <c r="AH24" s="12">
+      <c r="AH24" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B25" s="9"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="5">
         <v>23</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="7">
         <v>1</v>
       </c>
       <c r="E25" s="5">
@@ -2796,28 +2796,28 @@
       <c r="AB25" s="5">
         <v>1</v>
       </c>
-      <c r="AC25" s="11">
+      <c r="AC25" s="6">
         <v>1</v>
       </c>
       <c r="AD25" s="5">
         <v>1</v>
       </c>
-      <c r="AE25" s="11">
+      <c r="AE25" s="6">
         <v>0</v>
       </c>
       <c r="AG25" s="5">
         <v>1</v>
       </c>
-      <c r="AH25" s="12">
+      <c r="AH25" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B26" s="9"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="5">
         <v>24</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="7">
         <v>1</v>
       </c>
       <c r="E26" s="5">
@@ -2892,28 +2892,28 @@
       <c r="AB26" s="5">
         <v>1</v>
       </c>
-      <c r="AC26" s="11">
+      <c r="AC26" s="6">
         <v>1</v>
       </c>
       <c r="AD26" s="5">
         <v>0</v>
       </c>
-      <c r="AE26" s="11">
+      <c r="AE26" s="6">
         <v>1</v>
       </c>
       <c r="AG26" s="5">
         <v>0</v>
       </c>
-      <c r="AH26" s="12">
+      <c r="AH26" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B27" s="9"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="5">
         <v>25</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="7">
         <v>1</v>
       </c>
       <c r="E27" s="5">
@@ -2988,28 +2988,28 @@
       <c r="AB27" s="5">
         <v>1</v>
       </c>
-      <c r="AC27" s="11">
+      <c r="AC27" s="6">
         <v>0</v>
       </c>
       <c r="AD27" s="5">
         <v>1</v>
       </c>
-      <c r="AE27" s="11">
+      <c r="AE27" s="6">
         <v>0</v>
       </c>
       <c r="AG27" s="5">
         <v>0</v>
       </c>
-      <c r="AH27" s="12">
+      <c r="AH27" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B28" s="9"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="5">
         <v>26</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="7">
         <v>1</v>
       </c>
       <c r="E28" s="5">
@@ -3084,28 +3084,28 @@
       <c r="AB28" s="5">
         <v>0</v>
       </c>
-      <c r="AC28" s="11">
+      <c r="AC28" s="6">
         <v>1</v>
       </c>
       <c r="AD28" s="5">
         <v>0</v>
       </c>
-      <c r="AE28" s="11">
+      <c r="AE28" s="6">
         <v>0</v>
       </c>
       <c r="AG28" s="5">
         <v>1</v>
       </c>
-      <c r="AH28" s="12">
+      <c r="AH28" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B29" s="9"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="5">
         <v>27</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="7">
         <v>1</v>
       </c>
       <c r="E29" s="5">
@@ -3180,28 +3180,28 @@
       <c r="AB29" s="5">
         <v>1</v>
       </c>
-      <c r="AC29" s="11">
+      <c r="AC29" s="6">
         <v>0</v>
       </c>
       <c r="AD29" s="5">
         <v>0</v>
       </c>
-      <c r="AE29" s="11">
+      <c r="AE29" s="6">
         <v>1</v>
       </c>
       <c r="AG29" s="5">
         <v>1</v>
       </c>
-      <c r="AH29" s="12">
+      <c r="AH29" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B30" s="9"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="5">
         <v>28</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="7">
         <v>1</v>
       </c>
       <c r="E30" s="5">
@@ -3276,28 +3276,28 @@
       <c r="AB30" s="5">
         <v>0</v>
       </c>
-      <c r="AC30" s="11">
+      <c r="AC30" s="6">
         <v>0</v>
       </c>
       <c r="AD30" s="5">
         <v>1</v>
       </c>
-      <c r="AE30" s="11">
+      <c r="AE30" s="6">
         <v>1</v>
       </c>
       <c r="AG30" s="5">
         <v>1</v>
       </c>
-      <c r="AH30" s="12">
+      <c r="AH30" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B31" s="9"/>
+      <c r="B31" s="11"/>
       <c r="C31" s="5">
         <v>29</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="7">
         <v>0</v>
       </c>
       <c r="E31" s="5">
@@ -3372,28 +3372,28 @@
       <c r="AB31" s="5">
         <v>0</v>
       </c>
-      <c r="AC31" s="11">
+      <c r="AC31" s="6">
         <v>1</v>
       </c>
       <c r="AD31" s="5">
         <v>1</v>
       </c>
-      <c r="AE31" s="11">
+      <c r="AE31" s="6">
         <v>1</v>
       </c>
       <c r="AG31" s="5">
         <v>0</v>
       </c>
-      <c r="AH31" s="12">
+      <c r="AH31" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B32" s="9"/>
+      <c r="B32" s="11"/>
       <c r="C32" s="5">
         <v>30</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="7">
         <v>1</v>
       </c>
       <c r="E32" s="5">
@@ -3468,28 +3468,28 @@
       <c r="AB32" s="5">
         <v>1</v>
       </c>
-      <c r="AC32" s="11">
+      <c r="AC32" s="6">
         <v>1</v>
       </c>
       <c r="AD32" s="5">
         <v>1</v>
       </c>
-      <c r="AE32" s="11">
+      <c r="AE32" s="6">
         <v>0</v>
       </c>
       <c r="AG32" s="5">
         <v>1</v>
       </c>
-      <c r="AH32" s="12">
+      <c r="AH32" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B33" s="9"/>
+      <c r="B33" s="11"/>
       <c r="C33" s="5">
         <v>31</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="7">
         <v>0</v>
       </c>
       <c r="E33" s="5">
@@ -3564,28 +3564,28 @@
       <c r="AB33" s="5">
         <v>1</v>
       </c>
-      <c r="AC33" s="11">
+      <c r="AC33" s="6">
         <v>1</v>
       </c>
       <c r="AD33" s="5">
         <v>0</v>
       </c>
-      <c r="AE33" s="11">
+      <c r="AE33" s="6">
         <v>1</v>
       </c>
       <c r="AG33" s="5">
         <v>0</v>
       </c>
-      <c r="AH33" s="12">
+      <c r="AH33" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B34" s="9"/>
+      <c r="B34" s="11"/>
       <c r="C34" s="5">
         <v>32</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="7">
         <v>0</v>
       </c>
       <c r="E34" s="5">
@@ -3660,28 +3660,28 @@
       <c r="AB34" s="5">
         <v>1</v>
       </c>
-      <c r="AC34" s="11">
+      <c r="AC34" s="6">
         <v>0</v>
       </c>
       <c r="AD34" s="5">
         <v>1</v>
       </c>
-      <c r="AE34" s="11">
+      <c r="AE34" s="6">
         <v>0</v>
       </c>
       <c r="AG34" s="5">
         <v>0</v>
       </c>
-      <c r="AH34" s="12">
+      <c r="AH34" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B35" s="9"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="5">
         <v>33</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="7">
         <v>1</v>
       </c>
       <c r="E35" s="5">
@@ -3756,28 +3756,28 @@
       <c r="AB35" s="5">
         <v>0</v>
       </c>
-      <c r="AC35" s="11">
+      <c r="AC35" s="6">
         <v>1</v>
       </c>
       <c r="AD35" s="5">
         <v>0</v>
       </c>
-      <c r="AE35" s="11">
+      <c r="AE35" s="6">
         <v>0</v>
       </c>
       <c r="AG35" s="5">
         <v>1</v>
       </c>
-      <c r="AH35" s="12">
+      <c r="AH35" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B36" s="9"/>
+      <c r="B36" s="11"/>
       <c r="C36" s="5">
         <v>34</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="7">
         <v>1</v>
       </c>
       <c r="E36" s="5">
@@ -3852,28 +3852,28 @@
       <c r="AB36" s="5">
         <v>1</v>
       </c>
-      <c r="AC36" s="11">
+      <c r="AC36" s="6">
         <v>0</v>
       </c>
       <c r="AD36" s="5">
         <v>0</v>
       </c>
-      <c r="AE36" s="11">
+      <c r="AE36" s="6">
         <v>1</v>
       </c>
       <c r="AG36" s="5">
         <v>1</v>
       </c>
-      <c r="AH36" s="12">
+      <c r="AH36" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B37" s="9"/>
+      <c r="B37" s="11"/>
       <c r="C37" s="5">
         <v>35</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="7">
         <v>1</v>
       </c>
       <c r="E37" s="5">
@@ -3948,28 +3948,28 @@
       <c r="AB37" s="5">
         <v>0</v>
       </c>
-      <c r="AC37" s="11">
+      <c r="AC37" s="6">
         <v>0</v>
       </c>
       <c r="AD37" s="5">
         <v>1</v>
       </c>
-      <c r="AE37" s="11">
+      <c r="AE37" s="6">
         <v>1</v>
       </c>
       <c r="AG37" s="5">
         <v>1</v>
       </c>
-      <c r="AH37" s="12">
+      <c r="AH37" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B38" s="9"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="5">
         <v>36</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="7">
         <v>0</v>
       </c>
       <c r="E38" s="5">
@@ -4044,28 +4044,28 @@
       <c r="AB38" s="5">
         <v>0</v>
       </c>
-      <c r="AC38" s="11">
+      <c r="AC38" s="6">
         <v>1</v>
       </c>
       <c r="AD38" s="5">
         <v>1</v>
       </c>
-      <c r="AE38" s="11">
+      <c r="AE38" s="6">
         <v>1</v>
       </c>
       <c r="AG38" s="5">
         <v>0</v>
       </c>
-      <c r="AH38" s="12">
+      <c r="AH38" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B39" s="9"/>
+      <c r="B39" s="11"/>
       <c r="C39" s="5">
         <v>37</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="7">
         <v>1</v>
       </c>
       <c r="E39" s="5">
@@ -4140,28 +4140,28 @@
       <c r="AB39" s="5">
         <v>1</v>
       </c>
-      <c r="AC39" s="11">
+      <c r="AC39" s="6">
         <v>1</v>
       </c>
       <c r="AD39" s="5">
         <v>1</v>
       </c>
-      <c r="AE39" s="11">
+      <c r="AE39" s="6">
         <v>0</v>
       </c>
       <c r="AG39" s="5">
         <v>1</v>
       </c>
-      <c r="AH39" s="12">
+      <c r="AH39" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B40" s="9"/>
+      <c r="B40" s="11"/>
       <c r="C40" s="5">
         <v>38</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="7">
         <v>0</v>
       </c>
       <c r="E40" s="5">
@@ -4236,28 +4236,28 @@
       <c r="AB40" s="5">
         <v>1</v>
       </c>
-      <c r="AC40" s="11">
+      <c r="AC40" s="6">
         <v>1</v>
       </c>
       <c r="AD40" s="5">
         <v>0</v>
       </c>
-      <c r="AE40" s="11">
+      <c r="AE40" s="6">
         <v>1</v>
       </c>
       <c r="AG40" s="5">
         <v>0</v>
       </c>
-      <c r="AH40" s="12">
+      <c r="AH40" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B41" s="9"/>
+      <c r="B41" s="11"/>
       <c r="C41" s="5">
         <v>39</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="7">
         <v>0</v>
       </c>
       <c r="E41" s="5">
@@ -4332,28 +4332,28 @@
       <c r="AB41" s="5">
         <v>1</v>
       </c>
-      <c r="AC41" s="11">
+      <c r="AC41" s="6">
         <v>0</v>
       </c>
       <c r="AD41" s="5">
         <v>1</v>
       </c>
-      <c r="AE41" s="11">
+      <c r="AE41" s="6">
         <v>0</v>
       </c>
       <c r="AG41" s="5">
         <v>0</v>
       </c>
-      <c r="AH41" s="12">
+      <c r="AH41" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B42" s="9"/>
+      <c r="B42" s="11"/>
       <c r="C42" s="5">
         <v>40</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="7">
         <v>1</v>
       </c>
       <c r="E42" s="5">
@@ -4428,28 +4428,28 @@
       <c r="AB42" s="5">
         <v>0</v>
       </c>
-      <c r="AC42" s="11">
+      <c r="AC42" s="6">
         <v>1</v>
       </c>
       <c r="AD42" s="5">
         <v>0</v>
       </c>
-      <c r="AE42" s="11">
+      <c r="AE42" s="6">
         <v>0</v>
       </c>
       <c r="AG42" s="5">
         <v>1</v>
       </c>
-      <c r="AH42" s="12">
+      <c r="AH42" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B43" s="9"/>
+      <c r="B43" s="11"/>
       <c r="C43" s="5">
         <v>41</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="7">
         <v>1</v>
       </c>
       <c r="E43" s="5">
@@ -4524,28 +4524,28 @@
       <c r="AB43" s="5">
         <v>1</v>
       </c>
-      <c r="AC43" s="11">
+      <c r="AC43" s="6">
         <v>0</v>
       </c>
       <c r="AD43" s="5">
         <v>0</v>
       </c>
-      <c r="AE43" s="11">
+      <c r="AE43" s="6">
         <v>1</v>
       </c>
       <c r="AG43" s="5">
         <v>1</v>
       </c>
-      <c r="AH43" s="12">
+      <c r="AH43" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B44" s="9"/>
+      <c r="B44" s="11"/>
       <c r="C44" s="5">
         <v>42</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="7">
         <v>1</v>
       </c>
       <c r="E44" s="5">
@@ -4620,28 +4620,28 @@
       <c r="AB44" s="5">
         <v>0</v>
       </c>
-      <c r="AC44" s="11">
+      <c r="AC44" s="6">
         <v>0</v>
       </c>
       <c r="AD44" s="5">
         <v>1</v>
       </c>
-      <c r="AE44" s="11">
+      <c r="AE44" s="6">
         <v>1</v>
       </c>
       <c r="AG44" s="5">
         <v>1</v>
       </c>
-      <c r="AH44" s="12">
+      <c r="AH44" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B45" s="9"/>
+      <c r="B45" s="11"/>
       <c r="C45" s="5">
         <v>43</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="7">
         <v>0</v>
       </c>
       <c r="E45" s="5">
@@ -4716,28 +4716,28 @@
       <c r="AB45" s="5">
         <v>0</v>
       </c>
-      <c r="AC45" s="11">
+      <c r="AC45" s="6">
         <v>1</v>
       </c>
       <c r="AD45" s="5">
         <v>1</v>
       </c>
-      <c r="AE45" s="11">
+      <c r="AE45" s="6">
         <v>1</v>
       </c>
       <c r="AG45" s="5">
         <v>0</v>
       </c>
-      <c r="AH45" s="12">
+      <c r="AH45" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B46" s="9"/>
+      <c r="B46" s="11"/>
       <c r="C46" s="5">
         <v>44</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="7">
         <v>1</v>
       </c>
       <c r="E46" s="5">
@@ -4812,28 +4812,28 @@
       <c r="AB46" s="5">
         <v>1</v>
       </c>
-      <c r="AC46" s="11">
+      <c r="AC46" s="6">
         <v>1</v>
       </c>
       <c r="AD46" s="5">
         <v>1</v>
       </c>
-      <c r="AE46" s="11">
+      <c r="AE46" s="6">
         <v>0</v>
       </c>
       <c r="AG46" s="5">
         <v>1</v>
       </c>
-      <c r="AH46" s="12">
+      <c r="AH46" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B47" s="9"/>
+      <c r="B47" s="11"/>
       <c r="C47" s="5">
         <v>45</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="7">
         <v>0</v>
       </c>
       <c r="E47" s="5">
@@ -4908,28 +4908,28 @@
       <c r="AB47" s="5">
         <v>1</v>
       </c>
-      <c r="AC47" s="11">
+      <c r="AC47" s="6">
         <v>1</v>
       </c>
       <c r="AD47" s="5">
         <v>0</v>
       </c>
-      <c r="AE47" s="11">
+      <c r="AE47" s="6">
         <v>1</v>
       </c>
       <c r="AG47" s="5">
         <v>0</v>
       </c>
-      <c r="AH47" s="12">
+      <c r="AH47" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B48" s="9"/>
+      <c r="B48" s="11"/>
       <c r="C48" s="5">
         <v>46</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="7">
         <v>0</v>
       </c>
       <c r="E48" s="5">
@@ -5004,28 +5004,28 @@
       <c r="AB48" s="5">
         <v>1</v>
       </c>
-      <c r="AC48" s="11">
+      <c r="AC48" s="6">
         <v>0</v>
       </c>
       <c r="AD48" s="5">
         <v>1</v>
       </c>
-      <c r="AE48" s="11">
+      <c r="AE48" s="6">
         <v>0</v>
       </c>
       <c r="AG48" s="5">
         <v>0</v>
       </c>
-      <c r="AH48" s="12">
+      <c r="AH48" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B49" s="9"/>
+      <c r="B49" s="11"/>
       <c r="C49" s="5">
         <v>47</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="7">
         <v>1</v>
       </c>
       <c r="E49" s="5">
@@ -5100,28 +5100,28 @@
       <c r="AB49" s="5">
         <v>0</v>
       </c>
-      <c r="AC49" s="11">
+      <c r="AC49" s="6">
         <v>1</v>
       </c>
       <c r="AD49" s="5">
         <v>0</v>
       </c>
-      <c r="AE49" s="11">
+      <c r="AE49" s="6">
         <v>0</v>
       </c>
       <c r="AG49" s="5">
         <v>1</v>
       </c>
-      <c r="AH49" s="12">
+      <c r="AH49" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B50" s="9"/>
+      <c r="B50" s="11"/>
       <c r="C50" s="5">
         <v>48</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="7">
         <v>1</v>
       </c>
       <c r="E50" s="5">
@@ -5196,28 +5196,28 @@
       <c r="AB50" s="5">
         <v>1</v>
       </c>
-      <c r="AC50" s="11">
+      <c r="AC50" s="6">
         <v>0</v>
       </c>
       <c r="AD50" s="5">
         <v>0</v>
       </c>
-      <c r="AE50" s="11">
+      <c r="AE50" s="6">
         <v>1</v>
       </c>
       <c r="AG50" s="5">
         <v>1</v>
       </c>
-      <c r="AH50" s="12">
+      <c r="AH50" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B51" s="9"/>
+      <c r="B51" s="11"/>
       <c r="C51" s="5">
         <v>49</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="7">
         <v>1</v>
       </c>
       <c r="E51" s="5">
@@ -5292,28 +5292,28 @@
       <c r="AB51" s="5">
         <v>0</v>
       </c>
-      <c r="AC51" s="11">
+      <c r="AC51" s="6">
         <v>0</v>
       </c>
       <c r="AD51" s="5">
         <v>1</v>
       </c>
-      <c r="AE51" s="11">
+      <c r="AE51" s="6">
         <v>1</v>
       </c>
       <c r="AG51" s="5">
         <v>1</v>
       </c>
-      <c r="AH51" s="12">
+      <c r="AH51" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B52" s="9"/>
+      <c r="B52" s="11"/>
       <c r="C52" s="5">
         <v>50</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="7">
         <v>0</v>
       </c>
       <c r="E52" s="5">
@@ -5388,28 +5388,28 @@
       <c r="AB52" s="5">
         <v>0</v>
       </c>
-      <c r="AC52" s="11">
+      <c r="AC52" s="6">
         <v>1</v>
       </c>
       <c r="AD52" s="5">
         <v>1</v>
       </c>
-      <c r="AE52" s="11">
+      <c r="AE52" s="6">
         <v>1</v>
       </c>
       <c r="AG52" s="5">
         <v>0</v>
       </c>
-      <c r="AH52" s="12">
+      <c r="AH52" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B53" s="9"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="5">
         <v>51</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="7">
         <v>1</v>
       </c>
       <c r="E53" s="5">
@@ -5484,28 +5484,28 @@
       <c r="AB53" s="5">
         <v>1</v>
       </c>
-      <c r="AC53" s="11">
+      <c r="AC53" s="6">
         <v>1</v>
       </c>
       <c r="AD53" s="5">
         <v>1</v>
       </c>
-      <c r="AE53" s="11">
+      <c r="AE53" s="6">
         <v>0</v>
       </c>
       <c r="AG53" s="5">
         <v>1</v>
       </c>
-      <c r="AH53" s="12">
+      <c r="AH53" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B54" s="9"/>
+      <c r="B54" s="11"/>
       <c r="C54" s="5">
         <v>52</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="7">
         <v>0</v>
       </c>
       <c r="E54" s="5">
@@ -5580,28 +5580,28 @@
       <c r="AB54" s="5">
         <v>1</v>
       </c>
-      <c r="AC54" s="11">
+      <c r="AC54" s="6">
         <v>1</v>
       </c>
       <c r="AD54" s="5">
         <v>0</v>
       </c>
-      <c r="AE54" s="11">
+      <c r="AE54" s="6">
         <v>1</v>
       </c>
       <c r="AG54" s="5">
         <v>0</v>
       </c>
-      <c r="AH54" s="12">
+      <c r="AH54" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B55" s="9"/>
+      <c r="B55" s="11"/>
       <c r="C55" s="5">
         <v>53</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="7">
         <v>0</v>
       </c>
       <c r="E55" s="5">
@@ -5676,28 +5676,28 @@
       <c r="AB55" s="5">
         <v>1</v>
       </c>
-      <c r="AC55" s="11">
+      <c r="AC55" s="6">
         <v>0</v>
       </c>
       <c r="AD55" s="5">
         <v>1</v>
       </c>
-      <c r="AE55" s="11">
+      <c r="AE55" s="6">
         <v>0</v>
       </c>
       <c r="AG55" s="5">
         <v>0</v>
       </c>
-      <c r="AH55" s="12">
+      <c r="AH55" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B56" s="9"/>
+      <c r="B56" s="11"/>
       <c r="C56" s="5">
         <v>54</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="7">
         <v>1</v>
       </c>
       <c r="E56" s="5">
@@ -5772,28 +5772,28 @@
       <c r="AB56" s="5">
         <v>0</v>
       </c>
-      <c r="AC56" s="11">
+      <c r="AC56" s="6">
         <v>1</v>
       </c>
       <c r="AD56" s="5">
         <v>0</v>
       </c>
-      <c r="AE56" s="11">
+      <c r="AE56" s="6">
         <v>0</v>
       </c>
       <c r="AG56" s="5">
         <v>1</v>
       </c>
-      <c r="AH56" s="12">
+      <c r="AH56" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B57" s="9"/>
+      <c r="B57" s="11"/>
       <c r="C57" s="5">
         <v>55</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="7">
         <v>1</v>
       </c>
       <c r="E57" s="5">
@@ -5868,28 +5868,28 @@
       <c r="AB57" s="5">
         <v>1</v>
       </c>
-      <c r="AC57" s="11">
+      <c r="AC57" s="6">
         <v>0</v>
       </c>
       <c r="AD57" s="5">
         <v>0</v>
       </c>
-      <c r="AE57" s="11">
+      <c r="AE57" s="6">
         <v>1</v>
       </c>
       <c r="AG57" s="5">
         <v>1</v>
       </c>
-      <c r="AH57" s="12">
+      <c r="AH57" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B58" s="9"/>
+      <c r="B58" s="11"/>
       <c r="C58" s="5">
         <v>56</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="7">
         <v>1</v>
       </c>
       <c r="E58" s="5">
@@ -5964,28 +5964,28 @@
       <c r="AB58" s="5">
         <v>0</v>
       </c>
-      <c r="AC58" s="11">
+      <c r="AC58" s="6">
         <v>0</v>
       </c>
       <c r="AD58" s="5">
         <v>1</v>
       </c>
-      <c r="AE58" s="11">
+      <c r="AE58" s="6">
         <v>1</v>
       </c>
       <c r="AG58" s="5">
         <v>1</v>
       </c>
-      <c r="AH58" s="12">
+      <c r="AH58" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B59" s="9"/>
+      <c r="B59" s="11"/>
       <c r="C59" s="5">
         <v>57</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="7">
         <v>0</v>
       </c>
       <c r="E59" s="5">
@@ -6060,28 +6060,28 @@
       <c r="AB59" s="5">
         <v>0</v>
       </c>
-      <c r="AC59" s="11">
+      <c r="AC59" s="6">
         <v>1</v>
       </c>
       <c r="AD59" s="5">
         <v>1</v>
       </c>
-      <c r="AE59" s="11">
+      <c r="AE59" s="6">
         <v>1</v>
       </c>
       <c r="AG59" s="5">
         <v>0</v>
       </c>
-      <c r="AH59" s="12">
+      <c r="AH59" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B60" s="9"/>
+      <c r="B60" s="11"/>
       <c r="C60" s="5">
         <v>58</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="7">
         <v>1</v>
       </c>
       <c r="E60" s="5">
@@ -6156,28 +6156,28 @@
       <c r="AB60" s="5">
         <v>1</v>
       </c>
-      <c r="AC60" s="11">
+      <c r="AC60" s="6">
         <v>1</v>
       </c>
       <c r="AD60" s="5">
         <v>1</v>
       </c>
-      <c r="AE60" s="11">
+      <c r="AE60" s="6">
         <v>0</v>
       </c>
       <c r="AG60" s="5">
         <v>1</v>
       </c>
-      <c r="AH60" s="12">
+      <c r="AH60" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B61" s="9"/>
+      <c r="B61" s="11"/>
       <c r="C61" s="5">
         <v>59</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="7">
         <v>0</v>
       </c>
       <c r="E61" s="5">
@@ -6252,28 +6252,28 @@
       <c r="AB61" s="5">
         <v>1</v>
       </c>
-      <c r="AC61" s="11">
+      <c r="AC61" s="6">
         <v>1</v>
       </c>
       <c r="AD61" s="5">
         <v>0</v>
       </c>
-      <c r="AE61" s="11">
+      <c r="AE61" s="6">
         <v>1</v>
       </c>
       <c r="AG61" s="5">
         <v>0</v>
       </c>
-      <c r="AH61" s="12">
+      <c r="AH61" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B62" s="9"/>
+      <c r="B62" s="11"/>
       <c r="C62" s="5">
         <v>60</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="7">
         <v>0</v>
       </c>
       <c r="E62" s="5">
@@ -6348,57 +6348,57 @@
       <c r="AB62" s="5">
         <v>1</v>
       </c>
-      <c r="AC62" s="11">
+      <c r="AC62" s="6">
         <v>0</v>
       </c>
       <c r="AD62" s="5">
         <v>1</v>
       </c>
-      <c r="AE62" s="11">
+      <c r="AE62" s="6">
         <v>0</v>
       </c>
       <c r="AG62" s="5">
         <v>0</v>
       </c>
-      <c r="AH62" s="12">
+      <c r="AH62" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-      <c r="V64" s="7"/>
-      <c r="W64" s="7"/>
-      <c r="X64" s="7"/>
-      <c r="Y64" s="7"/>
-      <c r="Z64" s="7"/>
-      <c r="AA64" s="7"/>
-      <c r="AB64" s="7"/>
-      <c r="AC64" s="7"/>
-      <c r="AD64" s="7"/>
-      <c r="AE64" s="7"/>
-      <c r="AF64" s="7"/>
-      <c r="AG64" s="7"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9"/>
+      <c r="R64" s="9"/>
+      <c r="S64" s="9"/>
+      <c r="T64" s="9"/>
+      <c r="U64" s="9"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="9"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="9"/>
+      <c r="Z64" s="9"/>
+      <c r="AA64" s="9"/>
+      <c r="AB64" s="9"/>
+      <c r="AC64" s="9"/>
+      <c r="AD64" s="9"/>
+      <c r="AE64" s="9"/>
+      <c r="AF64" s="9"/>
+      <c r="AG64" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
